--- a/Assets/Resources/CSV/Equipment.xlsx
+++ b/Assets/Resources/CSV/Equipment.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UNITY GAME\类银河恶魔城\Assets\Data\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UNITY GAME\类银河恶魔城\Assets\Resources\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FA1366-CDDE-4CFE-9848-4E40BE21F523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5039C9EF-A625-4137-AB59-E73EC2394590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{28249393-CEE7-42CB-BEDD-967AC727C555}"/>
   </bookViews>
@@ -1405,7 +1405,7 @@
         <v>17</v>
       </c>
       <c r="D25" s="5">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>18</v>
